--- a/public/upload/report/REKAP TOTAL NILAI KPI YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 09 TAHUN 2026 .xlsx
+++ b/public/upload/report/REKAP TOTAL NILAI KPI YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 09 TAHUN 2026 .xlsx
@@ -1012,14 +1012,14 @@
         <v>16</v>
       </c>
       <c r="C6" s="3">
-        <v>7.0</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3">
-        <v>23.6</v>
+        <v>85.0</v>
       </c>
       <c r="E6" s="3">
         <f>AVERAGE(C6:D6)</f>
-        <v>15.3</v>
+        <v>42.5</v>
       </c>
       <c r="F6" s="3" t="str">
         <f>IF(E6&gt;=90,"Sangat Baik",IF(E6&gt;=80,"Baik",IF(E6&gt;=70,"Cukup",IF(E6&gt;=60,"Kurang","Perlu Pembinaan"))))</f>
@@ -1027,30 +1027,30 @@
       </c>
       <c r="G6" s="3">
         <f>IF(E6&gt;=90,100%,IF(E6&gt;=80,90%,IF(E6&gt;=70,80%,IF(E6&gt;=60,70%,IF(E6&gt;=50,60%,IF(E6&gt;=40,50%,IF(E6&gt;=30,40%,30%)))))))</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="4">
         <v>200000</v>
       </c>
       <c r="I6" s="4">
         <f>H6*G6</f>
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="J6" s="4">
-        <v>20000.0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4">
-        <v>10000.0</v>
+        <v>0</v>
       </c>
       <c r="L6" s="4">
-        <v>10000.0</v>
+        <v>0</v>
       </c>
       <c r="M6" s="4">
-        <v>20000.0</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4">
         <f>SUM(I6:M6)</f>
-        <v>120000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1159,14 +1159,14 @@
         <v>19</v>
       </c>
       <c r="C9" s="3">
-        <v>12.0</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3">
-        <v>35.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <f>AVERAGE(C9:D9)</f>
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="str">
         <f>IF(E9&gt;=90,"Sangat Baik",IF(E9&gt;=80,"Baik",IF(E9&gt;=70,"Cukup",IF(E9&gt;=60,"Kurang","Perlu Pembinaan"))))</f>

--- a/public/upload/report/REKAP TOTAL NILAI KPI YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 09 TAHUN 2026 .xlsx
+++ b/public/upload/report/REKAP TOTAL NILAI KPI YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 09 TAHUN 2026 .xlsx
@@ -1012,14 +1012,14 @@
         <v>16</v>
       </c>
       <c r="C6" s="3">
-        <v>0</v>
+        <v>13.0</v>
       </c>
       <c r="D6" s="3">
-        <v>85.0</v>
+        <v>16.68</v>
       </c>
       <c r="E6" s="3">
         <f>AVERAGE(C6:D6)</f>
-        <v>42.5</v>
+        <v>14.84</v>
       </c>
       <c r="F6" s="3" t="str">
         <f>IF(E6&gt;=90,"Sangat Baik",IF(E6&gt;=80,"Baik",IF(E6&gt;=70,"Cukup",IF(E6&gt;=60,"Kurang","Perlu Pembinaan"))))</f>
@@ -1027,14 +1027,14 @@
       </c>
       <c r="G6" s="3">
         <f>IF(E6&gt;=90,100%,IF(E6&gt;=80,90%,IF(E6&gt;=70,80%,IF(E6&gt;=60,70%,IF(E6&gt;=50,60%,IF(E6&gt;=40,50%,IF(E6&gt;=30,40%,30%)))))))</f>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="4">
         <v>200000</v>
       </c>
       <c r="I6" s="4">
         <f>H6*G6</f>
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="N6" s="4">
         <f>SUM(I6:M6)</f>
-        <v>100000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="7" spans="1:14">
